--- a/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
+++ b/InputData/bldgs/EoCEDwEC/Elast of Component E Demand wrt E Cost.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Dropbox (Energy Innovation)\Desktop\Vensim files from GitHub\EPS US\InputData\bldgs\EoCEDwEC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\bldgs\EoCEDwEC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67715FF-ECB8-403C-85D4-482D3A4407C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FBD62E1-8344-41DD-9A32-23621A92430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="825" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18705" yWindow="45" windowWidth="19905" windowHeight="19980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>EoCEDwEC Elasticity of Component Energy Demand wrt Energy Cost</t>
   </si>
@@ -180,6 +181,9 @@
     <t>Price Elasticities for Energy Use in Buildings of the United States</t>
   </si>
   <si>
+    <t>Appendix</t>
+  </si>
+  <si>
     <t>We use same-price, long-run elasticities minus the 3-year short-run elasticities.</t>
   </si>
   <si>
@@ -189,24 +193,19 @@
     <t>all timescales.  So, the portion of the long-run elasticitiy represented by the 3-year elasticity</t>
   </si>
   <si>
-    <t>This is a subset of Table 1 that includes only values from AEO2020 (not AEO99).</t>
-  </si>
-  <si>
-    <t>page 3: Table 1, Table 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Note from April 2023 - there has not been an updated version of this report. This is the most recent own-price elasticity data </t>
+    <t>This is a subset of Table 1 that includes only values from AEO2003 (not AEO99).</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -214,7 +213,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -222,7 +221,21 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -386,9 +399,6 @@
   <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -420,10 +430,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -438,59 +451,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>342129</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>94349</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39E86501-9ED3-7297-E799-C43233564A9A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6543675" y="161925"/>
-          <a:ext cx="6171429" cy="7209524"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -528,9 +492,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -563,26 +527,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -615,26 +562,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -809,17 +739,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="67.42578125" customWidth="1"/>
+    <col min="2" max="2" width="67.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -827,132 +757,133 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="23">
         <v>2021</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
@@ -963,268 +894,263 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="16.875" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="3" max="3" width="10.375" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="12.625" customWidth="1"/>
+    <col min="7" max="7" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+    <row r="4" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="4" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="4" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="G6" s="16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7">
-        <v>-0.13</v>
+      <c r="B7" s="6">
+        <v>-0.12</v>
       </c>
       <c r="C7">
-        <v>-0.22</v>
-      </c>
-      <c r="D7" s="8">
-        <v>-0.26</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.5</v>
+        <v>-0.21</v>
+      </c>
+      <c r="D7" s="7">
+        <v>-0.25</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.28000000000000003</v>
       </c>
       <c r="F7">
-        <v>0.03</v>
-      </c>
-      <c r="G7" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="G7" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7">
-        <v>-0.08</v>
+      <c r="B8" s="6">
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="C8">
         <v>-0.13</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>-0.15</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.1</v>
+      <c r="E8" s="6">
+        <v>0.03</v>
       </c>
       <c r="F8">
-        <v>-0.23</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+        <v>-0.21</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="9">
-        <v>-0.09</v>
-      </c>
-      <c r="C9" s="10">
-        <v>-0.16</v>
-      </c>
-      <c r="D9" s="11">
-        <v>-0.19</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="B9" s="8">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="C9" s="9">
+        <v>-0.12</v>
+      </c>
+      <c r="D9" s="10">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="10">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6">
+        <v>-0.11</v>
+      </c>
+      <c r="C14">
+        <v>-0.18</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-0.22</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.33</v>
+      </c>
+      <c r="F14">
+        <v>0.09</v>
+      </c>
+      <c r="G14" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6">
+        <v>-0.15</v>
+      </c>
+      <c r="C15">
+        <v>-0.25</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="F15">
+        <v>-0.57999999999999996</v>
+      </c>
+      <c r="G15" s="7">
         <v>0.02</v>
       </c>
-      <c r="F9" s="10">
-        <v>0.02</v>
-      </c>
-      <c r="G9" s="11">
+    </row>
+    <row r="16" spans="1:7" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C16" s="9">
         <v>-0.24</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="C14">
-        <v>-0.13</v>
-      </c>
-      <c r="D14" s="8">
-        <v>-0.15</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="F14">
-        <v>0.01</v>
-      </c>
-      <c r="G14" s="8">
+      <c r="D16" s="10">
+        <v>-0.28999999999999998</v>
+      </c>
+      <c r="E16" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="C15">
-        <v>-0.18</v>
-      </c>
-      <c r="D15" s="8">
-        <v>-0.25</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="F15">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="9">
-        <v>-0.13</v>
-      </c>
-      <c r="C16" s="10">
-        <v>-0.22</v>
-      </c>
-      <c r="D16" s="11">
-        <v>-0.26</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0</v>
-      </c>
-      <c r="F16" s="10">
-        <v>0.01</v>
-      </c>
-      <c r="G16" s="11">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>53</v>
+      <c r="F16" s="9">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="10">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1234,96 +1160,96 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.140625" customWidth="1"/>
-    <col min="2" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.125" customWidth="1"/>
+    <col min="2" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
+    <row r="1" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="21">
         <f>'EIA Table 1'!E7-'EIA Table 1'!D7</f>
-        <v>-0.24</v>
-      </c>
-      <c r="C2" s="22">
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="C2" s="21">
         <f>B2</f>
-        <v>-0.24</v>
-      </c>
-      <c r="D2" s="22">
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="D2" s="21">
         <f>'EIA Table 1'!E14-'EIA Table 1'!D14</f>
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.11000000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="20">
         <f>B5</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="C3" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="C3" s="20">
         <f t="shared" ref="C3:C6" si="0">B3</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="D3" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="D3" s="20">
         <f>D5</f>
-        <v>-3.999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="21">
         <f>'EIA Table 1'!F8-'EIA Table 1'!D8</f>
-        <v>-8.0000000000000016E-2</v>
-      </c>
-      <c r="C4" s="22">
+        <v>-0.06</v>
+      </c>
+      <c r="C4" s="21">
         <f t="shared" si="0"/>
-        <v>-8.0000000000000016E-2</v>
-      </c>
-      <c r="D4" s="22">
+        <v>-0.06</v>
+      </c>
+      <c r="D4" s="21">
         <f>'EIA Table 1'!F15-'EIA Table 1'!D15</f>
-        <v>-3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.27999999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="21">
         <f>'EIA Table 1'!G9-'EIA Table 1'!D9</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="C5" s="22">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="C5" s="21">
         <f t="shared" si="0"/>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="D5" s="22">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="D5" s="21">
         <f>'EIA Table 1'!G16-'EIA Table 1'!D16</f>
-        <v>-3.999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1338,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1352,78 +1278,250 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <f>B5</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="C8" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="C8" s="20">
         <f t="shared" ref="C8:D8" si="1">C5</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="D8" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="D8" s="20">
         <f t="shared" si="1"/>
-        <v>-3.999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <f>B5</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="C9" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="C9" s="20">
         <f t="shared" ref="C9:D9" si="2">C5</f>
-        <v>-4.9999999999999989E-2</v>
-      </c>
-      <c r="D9" s="21">
+        <v>-7.9999999999999988E-2</v>
+      </c>
+      <c r="D9" s="20">
         <f t="shared" si="2"/>
-        <v>-3.999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21">
+      <c r="B10" s="20">
         <f>B4</f>
-        <v>-8.0000000000000016E-2</v>
-      </c>
-      <c r="C10" s="21">
+        <v>-0.06</v>
+      </c>
+      <c r="C10" s="20">
         <f t="shared" ref="C10:D10" si="3">C4</f>
-        <v>-8.0000000000000016E-2</v>
-      </c>
-      <c r="D10" s="21">
+        <v>-0.06</v>
+      </c>
+      <c r="D10" s="20">
         <f t="shared" si="3"/>
-        <v>-3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>-0.27999999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <f>B2</f>
-        <v>-0.24</v>
-      </c>
-      <c r="C11" s="21">
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="C11" s="20">
         <f t="shared" ref="C11:D11" si="4">C2</f>
-        <v>-0.24</v>
-      </c>
-      <c r="D11" s="21">
+        <v>-3.0000000000000027E-2</v>
+      </c>
+      <c r="D11" s="20">
         <f t="shared" si="4"/>
-        <v>-0.03</v>
+        <v>-0.11000000000000001</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="C3" formula="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4986AE1F-586A-4325-87F9-78F8F3D1B43B}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF2C730C-3181-4F0E-B421-673A5D72627D}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6F7612B-D3D6-40E3-A7AB-F2A5BFA63F78}"/>
 </file>